--- a/excel-files/CALOOCAN/M.B. ASISTIO SR. HIGH SCHOOL - UNIT I.xlsx
+++ b/excel-files/CALOOCAN/M.B. ASISTIO SR. HIGH SCHOOL - UNIT I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D2C7418-1397-4A44-85E1-5BEABFDE21EC}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{175C15D8-DFCD-4427-99E0-E30E39D6219F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3504,7 +3504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" hidden="1" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="4" spans="1:8" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" hidden="1" customHeight="1">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:8" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3604,12 +3604,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1">
+    <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" hidden="1" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:8" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3709,12 +3709,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1">
+    <row r="13" spans="1:8">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" hidden="1" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" hidden="1" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" hidden="1" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:8" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1">
+    <row r="20" spans="1:8">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3844,7 +3844,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:8" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4034,7 +4034,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" hidden="1" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:8" ht="12" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4224,7 +4224,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:8" ht="21" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:8" ht="20.25" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:8" ht="17.25" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:8" ht="20.25" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:8" ht="21.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:8" ht="25.5" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:8" ht="18.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:8" ht="35.25" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:8" ht="39" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -5565,8 +5565,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F91:F98 F51:F59 F71:F79 F81:F89 F2:F6 F8:F12 F61:F69" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5581,7 +5581,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5806,7 +5806,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5944,7 +5944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" ht="19.149999999999999">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6289,7 +6289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6371,7 +6371,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" ht="19.149999999999999">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6923,7 +6923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6937,7 +6937,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7006,7 +7006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7420,7 +7420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" ht="19.149999999999999">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7572,7 +7572,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7710,7 +7710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8207,7 +8207,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8828,7 +8828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8842,7 +8842,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" ht="19.149999999999999">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8980,7 +8980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9118,7 +9118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9325,7 +9325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9394,7 +9394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9463,7 +9463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -13711,186 +13711,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C112:C127 C5:C12 C73:C81 C63:C71 C83:C91 C93:C101 C103:C110" name="Textbooks"/>
@@ -13904,15 +13724,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 X112:X127 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 F73:F81" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G103:G110 G83:G91 G93:G101 G73:G81" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R126 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{48CA286E-C6C0-484B-9D5B-FAA4C6CB5307}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13927,7 +13750,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14073,7 +13896,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="38.25" hidden="1">
+    <row r="3" spans="1:27" ht="38.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14142,7 +13965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="4" spans="1:27" ht="19.149999999999999">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14211,7 +14034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14280,7 +14103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14349,7 +14172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14418,7 +14241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14487,7 +14310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14556,7 +14379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14625,8 +14448,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" s="7" customFormat="1"/>
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14695,7 +14518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" ht="19.149999999999999">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14764,7 +14587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14833,7 +14656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14902,7 +14725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14971,7 +14794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -15040,7 +14863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15109,7 +14932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15178,8 +15001,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" s="7" customFormat="1"/>
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15248,7 +15071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" ht="19.149999999999999">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15317,7 +15140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15386,7 +15209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15455,7 +15278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15524,7 +15347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15593,7 +15416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15662,7 +15485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15731,7 +15554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15800,8 +15623,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" s="7" customFormat="1"/>
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15870,7 +15693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" ht="19.149999999999999">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15939,7 +15762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16008,7 +15831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16077,7 +15900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16146,7 +15969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16215,7 +16038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16284,7 +16107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16353,7 +16176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16422,7 +16245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16491,7 +16314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16560,8 +16383,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16630,7 +16453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16699,7 +16522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16768,7 +16591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16837,7 +16660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16906,7 +16729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16975,7 +16798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -17044,7 +16867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -17113,7 +16936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17182,7 +17005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" ht="19.149999999999999">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17251,7 +17074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17320,8 +17143,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" s="7" customFormat="1"/>
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17390,7 +17213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17459,7 +17282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17528,7 +17351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17597,7 +17420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17666,7 +17489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17735,7 +17558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17804,7 +17627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" ht="19.149999999999999">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17873,7 +17696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17942,7 +17765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="64" spans="1:27" ht="19.149999999999999">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -18011,7 +17834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -22670,186 +22493,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C103:C113 C91:C101 C115:C122 C67:C77 C79:C89" name="Textbooks"/>
@@ -22863,12 +22506,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 M115:M122 M103:M113 G103:G113 G91:G101 Y103:Y113 S91:S101 S103:S113 M91:M101 Y91:Y101" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X103:X113 R91:R101 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 F103:F113 L91:L101 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 L103:L113 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 X91:X101" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10" xr:uid="{6877231B-F5CD-4BCF-B210-BAE30A241275}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
